--- a/data/trans_dic/IP24_R2_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R2_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 18,66</t>
+          <t>11,65; 23,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,78; 24,09</t>
+          <t>8,07; 17,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,55; 20,03</t>
+          <t>11,28; 19,25</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,86; 26,45</t>
+          <t>7,44; 17,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,05; 20,4</t>
+          <t>12,65; 27,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,8; 20,93</t>
+          <t>11,3; 20,3</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,09; 27,18</t>
+          <t>6,14; 18,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 26,16</t>
+          <t>7,73; 24,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,26; 22,87</t>
+          <t>8,8; 19,87</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,77; 59,35</t>
+          <t>14,26; 23,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,54; 25,53</t>
+          <t>19,49; 30,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,55; 43,03</t>
+          <t>18,12; 25,3</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,26; 21,83</t>
+          <t>12,54; 35,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,29; 38,32</t>
+          <t>10,18; 19,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 29,37</t>
+          <t>13,14; 27,77</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,09; 28,87</t>
+          <t>6,79; 21,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,48; 21,72</t>
+          <t>9,06; 23,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,96; 21,97</t>
+          <t>9,81; 19,56</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,02; 33,5</t>
+          <t>14,19; 20,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,38; 22,31</t>
+          <t>15,34; 20,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,75; 26,46</t>
+          <t>15,29; 19,25</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13580</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23960</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37540</t>
+          <t>34206</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8507; 19492</t>
+          <t>14246; 28744</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16082; 32882</t>
+          <t>8303; 18415</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27840; 48263</t>
+          <t>25410; 43348</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>18071</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11959</t>
+          <t>17985</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30030</t>
+          <t>28928</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12100; 24889</t>
+          <t>6765; 16175</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7653; 19393</t>
+          <t>12153; 26065</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22312; 39586</t>
+          <t>21129; 37967</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>14124</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4715; 14095</t>
+          <t>3455; 10448</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4816; 16504</t>
+          <t>4135; 12869</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11791; 26283</t>
+          <t>9665; 21812</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>81405</t>
+          <t>38257</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>43994</t>
+          <t>43246</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125399</t>
+          <t>81504</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55946; 128830</t>
+          <t>28517; 47798</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33578; 55155</t>
+          <t>34687; 54297</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97663; 186384</t>
+          <t>68506; 95632</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19238</t>
+          <t>29317</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>35811</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55049</t>
+          <t>46882</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13448; 26074</t>
+          <t>18548; 52861</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23189; 62160</t>
+          <t>12082; 23697</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41066; 82708</t>
+          <t>35052; 74051</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>10703</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22130</t>
+          <t>19045</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7642; 19893</t>
+          <t>4638; 14731</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5383; 15643</t>
+          <t>6377; 16331</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15438; 30949</t>
+          <t>13598; 27118</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>181</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>153353</t>
+          <t>114450</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>134359</t>
+          <t>110239</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>287712</t>
+          <t>224688</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>124752; 219731</t>
+          <t>97321; 143076</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>114558; 166192</t>
+          <t>95016; 126736</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>248633; 370675</t>
+          <t>199585; 251283</t>
         </is>
       </c>
     </row>
